--- a/Master/2268r3/2268r3 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2268r3/2268r3 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -894,262 +894,342 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>1.119</v>
+        <v>2.23</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3.4642</v>
+        <v>3.4096</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.0968</v>
+        <v>-1.5763</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>4.12</v>
+        <v>4.232</v>
       </c>
       <c r="B24" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.5508</v>
+        <v>3.4098</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-0.0424</v>
+        <v>-1.7202</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>3.121</v>
+        <v>3.233</v>
       </c>
       <c r="B25" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3.6518</v>
+        <v>3.4105</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.262</v>
+        <v>-1.9128</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.0266</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>6.122</v>
+        <v>1.231</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.722</v>
+        <v>3.4107</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>-0.2211</v>
+        <v>-1.7587</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.0128</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>5.123</v>
+        <v>1.119</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3.7908</v>
+        <v>3.4642</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.4484</v>
+        <v>-0.0968</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0189</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>2.124</v>
+        <v>4.12</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.8452</v>
+        <v>3.5508</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>-0.6861</v>
+        <v>-0.0424</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>1.125</v>
+        <v>3.121</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3.8773</v>
+        <v>3.6518</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.8982</v>
+        <v>-0.262</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0266</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>4.126</v>
+        <v>6.122</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.9092</v>
+        <v>3.722</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>-0.9176</v>
+        <v>-0.2211</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.0035</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>3.127</v>
+        <v>5.123</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3.913</v>
+        <v>3.7908</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-1.0805</v>
+        <v>-0.4484</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.0027</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>6.128</v>
+        <v>2.124</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>3.9303</v>
+        <v>3.8452</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>-1.1032</v>
+        <v>-0.6861</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.0021</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>5.129</v>
+        <v>1.125</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3.9307</v>
+        <v>3.8773</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-1.2414</v>
+        <v>-0.8982</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0012</v>
+        <v>0.009299999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
+        <v>4.126</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>3.9092</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>-0.9176</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0.0035</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>3.127</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>-1.0805</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>0.0027</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>6.128</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>3.9303</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>-1.1032</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>5.129</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>3.9307</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>-1.2414</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>0.0012</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
         <v>1.131</v>
       </c>
-      <c r="B34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
+      <c r="B38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
         <v>3.9363</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E38" s="7" t="n">
         <v>-1.6948</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F38" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="E36" s="8" t="inlineStr">
+    <row r="40">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="E37" s="8" t="inlineStr">
+      <c r="F40" s="9" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>0.9745</v>
+      <c r="F41" s="10" t="n">
+        <v>0.9749</v>
       </c>
     </row>
   </sheetData>
